--- a/artfynd/A 49997-2021 artfynd.xlsx
+++ b/artfynd/A 49997-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49997-2021 artfynd.xlsx
+++ b/artfynd/A 49997-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107508832</v>
+        <v>107508831</v>
       </c>
       <c r="B2" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603756.9749149858</v>
+        <v>603757</v>
       </c>
       <c r="R2" t="n">
-        <v>6942466.944883056</v>
+        <v>6942467</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -748,19 +743,9 @@
           <t>2019-01-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-01-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107508834</v>
+        <v>107508833</v>
       </c>
       <c r="B3" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603756.9749149858</v>
+        <v>603757</v>
       </c>
       <c r="R3" t="n">
-        <v>6942466.944883056</v>
+        <v>6942467</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -869,19 +849,9 @@
           <t>2019-01-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-01-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,37 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107508831</v>
+        <v>107508832</v>
       </c>
       <c r="B4" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603756.9749149858</v>
+        <v>603757</v>
       </c>
       <c r="R4" t="n">
-        <v>6942466.944883056</v>
+        <v>6942467</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -990,19 +955,9 @@
           <t>2019-01-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-01-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107508833</v>
+        <v>107508834</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603756.9749149858</v>
+        <v>603757</v>
       </c>
       <c r="R5" t="n">
-        <v>6942466.944883056</v>
+        <v>6942467</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1111,19 +1061,9 @@
           <t>2019-01-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-01-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 49997-2021 artfynd.xlsx
+++ b/artfynd/A 49997-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107508831</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107508833</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107508832</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,8 +1116,19 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107508834</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>